--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StockMovement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D605E360-C135-46CC-B9D4-0BC7394200D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13627D42-B61B-401F-A67B-EE71A0B676F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5D666413-20EC-4276-AA61-3C31490D1C78}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
   <si>
     <t>รูปประกอบ</t>
   </si>
@@ -47,9 +47,6 @@
     <t>ชื่อแบร์น</t>
   </si>
   <si>
-    <t>รหัส</t>
-  </si>
-  <si>
     <t>ชื่อเรียกภาษาไทย</t>
   </si>
   <si>
@@ -201,6 +198,12 @@
   </si>
   <si>
     <t>จำนวน min สั่งซื้อ</t>
+  </si>
+  <si>
+    <t>รหัสแบร์น</t>
+  </si>
+  <si>
+    <t>รหัสสินค้า</t>
   </si>
 </sst>
 </file>
@@ -273,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -307,6 +310,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1047,10 +1053,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE1E03F-5485-4965-9EF9-5B5FDFCABC8C}">
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="4" max="4" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="51" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1061,387 +1071,422 @@
         <v>2</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="2"/>
+      <c r="N1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="10" t="s">
+      <c r="Q1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="R1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="4"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="4"/>
     </row>
-    <row r="2" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="12" t="str">
+        <f>G2&amp;"-"&amp;H2&amp;"-"&amp;I2&amp;"-"&amp;J2</f>
+        <v>SN-CW-BC-001</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="N2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="3">
-        <v>0</v>
       </c>
       <c r="P2" s="3">
         <v>0</v>
       </c>
       <c r="Q2" s="3">
+        <v>0</v>
+      </c>
+      <c r="R2" s="3">
         <v>6</v>
       </c>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="7"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="7"/>
     </row>
-    <row r="3" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="12" t="str">
+        <f t="shared" ref="E3:E9" si="0">G3&amp;H3&amp;I3&amp;J3</f>
+        <v>SNCWKT001</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="6"/>
+      <c r="J3" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="6"/>
+      <c r="N3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="3">
+      <c r="P3" s="3">
         <v>5</v>
       </c>
-      <c r="P3" s="3">
+      <c r="Q3" s="3">
         <v>2</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="R3" s="3">
         <v>0</v>
       </c>
-      <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
     </row>
-    <row r="4" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>SNCWKT002</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="6"/>
+      <c r="N4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" s="3">
+      <c r="P4" s="3">
         <v>4</v>
       </c>
-      <c r="P4" s="3">
+      <c r="Q4" s="3">
         <v>2</v>
       </c>
-      <c r="Q4" s="3"/>
-      <c r="X4" s="4"/>
+      <c r="R4" s="3"/>
       <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>SNCWSP001</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="6"/>
+      <c r="J5" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
-      <c r="M5" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="M5" s="6"/>
       <c r="N5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" s="3">
+        <v>28</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" s="3">
         <v>6</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <v>2</v>
       </c>
-      <c r="Q5" s="3"/>
-      <c r="X5" s="4"/>
+      <c r="R5" s="3"/>
       <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>SNCWSP002</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="6"/>
+      <c r="I6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
-      <c r="M6" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="M6" s="6"/>
       <c r="N6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O6" s="3">
+        <v>28</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6" s="3">
         <v>4</v>
       </c>
-      <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
-      <c r="X6" s="4"/>
+      <c r="R6" s="3"/>
       <c r="Y6" s="4"/>
+      <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>SNCWSP003</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
-      <c r="M7" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="M7" s="6"/>
       <c r="N7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="3">
+        <v>28</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P7" s="3">
         <v>6</v>
       </c>
-      <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
-      <c r="X7" s="4"/>
+      <c r="R7" s="3"/>
       <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
     </row>
-    <row r="8" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>SNCWSP004</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="M8" s="6"/>
       <c r="N8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8" s="3">
+        <v>28</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" s="3">
         <v>5</v>
       </c>
-      <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="X8" s="4"/>
+      <c r="R8" s="3"/>
       <c r="Y8" s="4"/>
+      <c r="Z8" s="4"/>
     </row>
-    <row r="9" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5"/>
       <c r="B9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="D9" s="3">
         <v>32857001</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>SNCWSP005</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
-      <c r="M9" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="M9" s="6"/>
       <c r="N9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="O9" s="3">
+        <v>28</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P9" s="3">
         <v>2</v>
       </c>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3">
         <v>1</v>
       </c>
-      <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StockMovement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13627D42-B61B-401F-A67B-EE71A0B676F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBAECCB-916A-43FA-9E11-9C53F421D837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5D666413-20EC-4276-AA61-3C31490D1C78}"/>
   </bookViews>
@@ -53,12 +53,6 @@
     <t>เลขลำดับ</t>
   </si>
   <si>
-    <t xml:space="preserve">ระบุทรัพย์สิน </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ตำแหน่งที่อยู่ </t>
-  </si>
-  <si>
     <t>ประเภทงาน</t>
   </si>
   <si>
@@ -185,15 +179,6 @@
     <t>ห้องน้ำไทร์ป ABC</t>
   </si>
   <si>
-    <t>โค๊ตหมวดหลัก</t>
-  </si>
-  <si>
-    <t>โค๊ตหมวดรอง</t>
-  </si>
-  <si>
-    <t>โค๊ตหมวดย่อย</t>
-  </si>
-  <si>
     <t>จำนวน max</t>
   </si>
   <si>
@@ -204,6 +189,21 @@
   </si>
   <si>
     <t>รหัสสินค้า</t>
+  </si>
+  <si>
+    <t>Code หมวดหลัก</t>
+  </si>
+  <si>
+    <t>Code หมวดรอง</t>
+  </si>
+  <si>
+    <t>Code ย่อย</t>
+  </si>
+  <si>
+    <t>เป็นทรัพย์สิน</t>
+  </si>
+  <si>
+    <t>ที่อยู่ปัจจุบันของทรัพย์สิน</t>
   </si>
 </sst>
 </file>
@@ -1071,47 +1071,47 @@
         <v>2</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="M1" s="2"/>
       <c r="N1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="10" t="s">
         <v>7</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>9</v>
       </c>
       <c r="Y1" s="8"/>
       <c r="Z1" s="4"/>
@@ -1126,34 +1126,34 @@
         <v>SN-CW-BC-001</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="N2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="O2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="P2" s="3">
         <v>0</v>
@@ -1171,38 +1171,38 @@
       <c r="A3" s="5"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="12" t="str">
+        <f t="shared" ref="E3:E9" si="0">G3&amp;"-"&amp;H3&amp;"-"&amp;I3&amp;"-"&amp;J3</f>
+        <v>SN-CW-KT-001</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="12" t="str">
-        <f t="shared" ref="E3:E9" si="0">G3&amp;H3&amp;I3&amp;J3</f>
-        <v>SNCWKT001</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P3" s="3">
         <v>5</v>
@@ -1223,31 +1223,31 @@
       <c r="D4" s="3"/>
       <c r="E4" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>SNCWKT002</v>
+        <v>SN-CW-KT-002</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P4" s="3">
         <v>4</v>
@@ -1263,36 +1263,36 @@
       <c r="A5" s="5"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>SNCWSP001</v>
+        <v>SN-CW-SP-001</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P5" s="3">
         <v>6</v>
@@ -1308,38 +1308,38 @@
       <c r="A6" s="5"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E6" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>SNCWSP002</v>
+        <v>SN-CW-SP-002</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P6" s="3">
         <v>4</v>
@@ -1353,38 +1353,38 @@
       <c r="A7" s="5"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>SNCWSP003</v>
+        <v>SN-CW-SP-003</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P7" s="3">
         <v>6</v>
@@ -1398,38 +1398,38 @@
       <c r="A8" s="5"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>SNCWSP004</v>
+        <v>SN-CW-SP-004</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P8" s="3">
         <v>5</v>
@@ -1442,41 +1442,41 @@
     <row r="9" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5"/>
       <c r="B9" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D9" s="3">
         <v>32857001</v>
       </c>
       <c r="E9" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>SNCWSP005</v>
+        <v>SN-CW-SP-005</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P9" s="3">
         <v>2</v>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StockMovement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBAECCB-916A-43FA-9E11-9C53F421D837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8243D3-576B-46DF-99F5-175695727C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5D666413-20EC-4276-AA61-3C31490D1C78}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="45">
   <si>
     <t>รูปประกอบ</t>
   </si>
@@ -53,12 +53,6 @@
     <t>เลขลำดับ</t>
   </si>
   <si>
-    <t>ประเภทงาน</t>
-  </si>
-  <si>
-    <t>ตำแหน่งที่ใช้</t>
-  </si>
-  <si>
     <t>นับจริง</t>
   </si>
   <si>
@@ -86,12 +80,6 @@
     <t>28/03/2026</t>
   </si>
   <si>
-    <t>อุปกรณ์ระเบียงห้อง</t>
-  </si>
-  <si>
-    <t>สั่งผิดใช้ไม่ได้</t>
-  </si>
-  <si>
     <t>rasland</t>
   </si>
   <si>
@@ -104,33 +92,18 @@
     <t>KT</t>
   </si>
   <si>
-    <t>อุปกรณ์อ่างล้างจาน</t>
-  </si>
-  <si>
-    <t>อ่างล้างจาน</t>
-  </si>
-  <si>
     <t xml:space="preserve">ปากกรองก็อกน้ำเกลียวใน </t>
   </si>
   <si>
     <t>002</t>
   </si>
   <si>
-    <t>อุปกรณ์ห้องน้ำ</t>
-  </si>
-  <si>
-    <t>ก็อกน้ำอ่างล้างหน้า</t>
-  </si>
-  <si>
     <t>สต็อปวาล์ว 4 หุน</t>
   </si>
   <si>
     <t>SP</t>
   </si>
   <si>
-    <t>ทางออกน้ำทุกจุด</t>
-  </si>
-  <si>
     <t>Hang</t>
   </si>
   <si>
@@ -140,9 +113,6 @@
     <t>หัวฉีดชำระ</t>
   </si>
   <si>
-    <t>ห้องน้ำ ไทร์ป A B C</t>
-  </si>
-  <si>
     <t>RA H811-H681</t>
   </si>
   <si>
@@ -152,9 +122,6 @@
     <t>003</t>
   </si>
   <si>
-    <t>ห้องน้ำ</t>
-  </si>
-  <si>
     <t>Ra 16cs02/chrome</t>
   </si>
   <si>
@@ -176,9 +143,6 @@
     <t>005</t>
   </si>
   <si>
-    <t>ห้องน้ำไทร์ป ABC</t>
-  </si>
-  <si>
     <t>จำนวน max</t>
   </si>
   <si>
@@ -204,6 +168,9 @@
   </si>
   <si>
     <t>ที่อยู่ปัจจุบันของทรัพย์สิน</t>
+  </si>
+  <si>
+    <t>ประเภท</t>
   </si>
 </sst>
 </file>
@@ -1053,14 +1020,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE1E03F-5485-4965-9EF9-5B5FDFCABC8C}">
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="4" width="8.69921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1071,52 +1038,49 @@
         <v>2</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M1" s="2"/>
       <c r="N1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="4"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1126,97 +1090,93 @@
         <v>SN-CW-BC-001</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>17</v>
+      <c r="N2" s="3" t="str">
+        <f>G2</f>
+        <v>SN</v>
+      </c>
+      <c r="O2" s="3">
+        <v>0</v>
       </c>
       <c r="P2" s="3">
         <v>0</v>
       </c>
       <c r="Q2" s="3">
-        <v>0</v>
-      </c>
-      <c r="R2" s="3">
         <v>6</v>
       </c>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="7"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="7"/>
     </row>
-    <row r="3" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E3" s="12" t="str">
         <f t="shared" ref="E3:E9" si="0">G3&amp;"-"&amp;H3&amp;"-"&amp;I3&amp;"-"&amp;J3</f>
         <v>SN-CW-KT-001</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
-      <c r="N3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>23</v>
+      <c r="N3" s="3" t="str">
+        <f t="shared" ref="N3:N9" si="1">G3</f>
+        <v>SN</v>
+      </c>
+      <c r="O3" s="3">
+        <v>5</v>
       </c>
       <c r="P3" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="3">
-        <v>2</v>
-      </c>
-      <c r="R3" s="3">
         <v>0</v>
       </c>
+      <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1226,44 +1186,42 @@
         <v>SN-CW-KT-002</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
-      <c r="N4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>27</v>
+      <c r="N4" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>SN</v>
+      </c>
+      <c r="O4" s="3">
+        <v>4</v>
       </c>
       <c r="P4" s="3">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="3">
         <v>2</v>
       </c>
-      <c r="R4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="12" t="str">
@@ -1271,181 +1229,173 @@
         <v>SN-CW-SP-001</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
-      <c r="N5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>30</v>
+      <c r="N5" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>SN</v>
+      </c>
+      <c r="O5" s="3">
+        <v>6</v>
       </c>
       <c r="P5" s="3">
-        <v>6</v>
-      </c>
-      <c r="Q5" s="3">
         <v>2</v>
       </c>
-      <c r="R5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>SN-CW-SP-002</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
-      <c r="N6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="P6" s="3">
+      <c r="N6" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>SN</v>
+      </c>
+      <c r="O6" s="3">
         <v>4</v>
       </c>
+      <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
+      <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>SN-CW-SP-003</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
-      <c r="N7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P7" s="3">
+      <c r="N7" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>SN</v>
+      </c>
+      <c r="O7" s="3">
         <v>6</v>
       </c>
+      <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
+      <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
     </row>
-    <row r="8" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E8" s="12" t="str">
         <f t="shared" si="0"/>
         <v>SN-CW-SP-004</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
-      <c r="N8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="N8" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>SN</v>
+      </c>
+      <c r="O8" s="3">
         <v>5</v>
       </c>
+      <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
+      <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
     </row>
-    <row r="9" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5"/>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D9" s="3">
         <v>32857001</v>
@@ -1455,38 +1405,36 @@
         <v>SN-CW-SP-005</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
-      <c r="N9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="N9" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>SN</v>
+      </c>
+      <c r="O9" s="3">
         <v>2</v>
       </c>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3">
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3">
         <v>1</v>
       </c>
+      <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StockMovement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8243D3-576B-46DF-99F5-175695727C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7692FCAA-DE4F-41F3-B1A6-CCDE6F61EFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5D666413-20EC-4276-AA61-3C31490D1C78}"/>
   </bookViews>
@@ -170,7 +170,7 @@
     <t>ที่อยู่ปัจจุบันของทรัพย์สิน</t>
   </si>
   <si>
-    <t>ประเภท</t>
+    <t>หมวดหมู่</t>
   </si>
 </sst>
 </file>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StockMovement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83F26D6-2EBD-40B6-A14F-0F5523CD3FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD28BCE-BF8D-4542-807F-99C1597D8504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5D666413-20EC-4276-AA61-3C31490D1C78}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="Data up lord" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data up lord'!$B$1:$P$60</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Data up lord'!$A$1:$X$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data up lord'!$B$1:$P$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Data up lord'!$A$1:$X$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="147">
   <si>
     <t>รูปประกอบ</t>
   </si>
@@ -482,103 +482,13 @@
   </si>
   <si>
     <t>กันซึมเหลว</t>
-  </si>
-  <si>
-    <t>5ลิตร</t>
-  </si>
-  <si>
-    <t>11035CG00MG19</t>
-  </si>
-  <si>
-    <t>น้ำยาไล่ความชื้น  TOA Moisture Guard</t>
-  </si>
-  <si>
-    <t>WL</t>
-  </si>
-  <si>
-    <t>11035CVKILL19</t>
-  </si>
-  <si>
-    <t>น้ำยากำจัดเชื้อรา ตะไคร่น้ำToa 113 Microkill</t>
-  </si>
-  <si>
-    <t>8kg</t>
-  </si>
-  <si>
-    <t>Ext</t>
-  </si>
-  <si>
-    <t>ทินเนอร์ EXTRA AAA 8 กก.</t>
-  </si>
-  <si>
-    <t>11kg</t>
-  </si>
-  <si>
-    <t>BRACO</t>
-  </si>
-  <si>
-    <t>11KG</t>
-  </si>
-  <si>
-    <t>ทินเนอร์ BARCO AAA 11 KG</t>
-  </si>
-  <si>
-    <t>pro expert</t>
-  </si>
-  <si>
-    <t>PM888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สีทาฝ้าเพดาน 1แกลลอน </t>
-  </si>
-  <si>
-    <t>CR</t>
-  </si>
-  <si>
-    <t>PM889</t>
-  </si>
-  <si>
-    <t>สีทาฝ้า TOA รุ่น PRO EXPERT ขนาด 9 ลิตร สีควันบุหรี่ #PM888</t>
-  </si>
-  <si>
-    <t>4SEASON</t>
-  </si>
-  <si>
-    <t>QUICK PRIMER</t>
-  </si>
-  <si>
-    <t>4SEASON QUICK PRIMER 5แกลลอน</t>
-  </si>
-  <si>
-    <t>GLIPTON</t>
-  </si>
-  <si>
-    <t>สีน้ำมันทำเทียบสี 8260</t>
-  </si>
-  <si>
-    <t>สีน้ำมันทำเทียบสี 8261</t>
-  </si>
-  <si>
-    <t>สีน้ำอะคิลิกทาภายในMercury</t>
-  </si>
-  <si>
-    <t>สีน้ำอะคิลิกทาภายในCoty's Eyes</t>
-  </si>
-  <si>
-    <t>สีน้ำอะคิลิกทาภายนอก 8260</t>
-  </si>
-  <si>
-    <t>สีน้ำอะคิลิกทาภายนอกHi Ho Silver</t>
-  </si>
-  <si>
-    <t>สีน้ำอะคิลิกทาภายในPrairie Smoke</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -590,6 +500,13 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="222"/>
@@ -1017,22 +934,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>159075</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>63115</xdr:rowOff>
+      <xdr:colOff>53076</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>55498</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1222375</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>1098550</xdr:rowOff>
+      <xdr:colOff>1270000</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1127126</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
+        <xdr:cNvPr id="21" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D623AC8-570C-4086-A527-C4E0B2EB5108}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{024EB5E6-9714-4152-9DC1-B25FF48001D7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1042,56 +959,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="159075" y="57799855"/>
-          <a:ext cx="1063300" cy="1035435"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>53076</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>55498</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1270000</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1127126</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{024EB5E6-9714-4152-9DC1-B25FF48001D7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1141,7 +1008,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1191,7 +1058,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1241,7 +1108,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1291,7 +1158,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1341,7 +1208,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1391,7 +1258,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1441,7 +1308,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1491,7 +1358,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1541,7 +1408,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1591,7 +1458,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1641,7 +1508,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1691,7 +1558,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1741,7 +1608,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1791,7 +1658,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1841,7 +1708,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1891,7 +1758,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1941,7 +1808,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1991,7 +1858,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2041,7 +1908,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2067,56 +1934,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>219074</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1068779</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>1057275</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 101">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07374E9D-E4CE-4623-99A2-85A8987E9D95}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="219074" y="55555515"/>
-          <a:ext cx="849705" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
@@ -2141,7 +1958,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2185,7 +2002,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2205,156 +2022,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1066800</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>1100914</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="129" name="Picture 128">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62CC990D-712E-446E-A124-52AB1BA5DD95}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="276225" y="53212365"/>
-          <a:ext cx="790575" cy="1053289"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1115588</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>1133475</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="158" name="Picture 157">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB04CB30-A402-4149-8399-7C2036763A34}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="200025" y="60051315"/>
-          <a:ext cx="915563" cy="1104900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>1032313</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="159" name="Picture 158">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A1AE583-C3F1-4B8D-964F-40AAB30FCC4E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="361950" y="61260990"/>
-          <a:ext cx="685800" cy="937063"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>95251</xdr:rowOff>
@@ -2379,7 +2046,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2429,7 +2096,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2479,7 +2146,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2529,7 +2196,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2579,7 +2246,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2629,7 +2296,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2679,7 +2346,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2729,7 +2396,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2779,7 +2446,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2829,7 +2496,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2879,7 +2546,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2929,7 +2596,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId44" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2979,7 +2646,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId45" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3005,106 +2672,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1009650</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>1067141</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="183" name="Picture 182">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88BE5C9E-3894-455B-BA1F-7FF052683AE2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="285750" y="54336315"/>
-          <a:ext cx="723900" cy="1038566"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>1064154</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="184" name="Picture 183">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{688220E6-8B83-4619-8216-07E7EA4F5264}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="219075" y="56660415"/>
-          <a:ext cx="809625" cy="997479"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>257176</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -3129,7 +2696,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId48" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3179,7 +2746,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId49" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3522,12 +3089,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5E0365-ECB3-4BF2-AA24-36F8492D38B5}">
-  <dimension ref="A1:X60"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr defaultColWidth="7.59765625" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
     <col min="2" max="3" width="6.8984375" style="11" customWidth="1"/>
-    <col min="4" max="5" width="9.59765625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="11" customWidth="1"/>
     <col min="6" max="6" width="11" style="11" customWidth="1"/>
     <col min="7" max="7" width="8.8984375" style="11" customWidth="1"/>
     <col min="8" max="8" width="9.09765625" style="11" customWidth="1"/>
@@ -3646,7 +3214,10 @@
       <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="2" t="str">
+        <f t="shared" ref="E3:E46" si="0">G3&amp;"-"&amp;H3&amp;"-"&amp;I3&amp;"-"&amp;J3</f>
+        <v>SN-CW-KT-001</v>
+      </c>
       <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
@@ -3665,7 +3236,7 @@
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="2" t="str">
-        <f t="shared" ref="M3:M60" si="0">G3</f>
+        <f t="shared" ref="M3:M46" si="1">G3</f>
         <v>SN</v>
       </c>
       <c r="N3" s="2">
@@ -3683,7 +3254,10 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="E4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-KT-002</v>
+      </c>
       <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
@@ -3702,7 +3276,7 @@
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N4" s="2">
@@ -3720,7 +3294,10 @@
         <v>13</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-001</v>
+      </c>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
@@ -3739,7 +3316,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N5" s="2">
@@ -3759,7 +3336,10 @@
       <c r="D6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-002</v>
+      </c>
       <c r="F6" s="2" t="s">
         <v>23</v>
       </c>
@@ -3778,7 +3358,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N6" s="2">
@@ -3796,7 +3376,10 @@
       <c r="D7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-003</v>
+      </c>
       <c r="F7" s="2" t="s">
         <v>25</v>
       </c>
@@ -3815,7 +3398,7 @@
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N7" s="2">
@@ -3833,7 +3416,10 @@
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-004</v>
+      </c>
       <c r="F8" s="2" t="s">
         <v>28</v>
       </c>
@@ -3852,7 +3438,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N8" s="2">
@@ -3872,7 +3458,10 @@
       <c r="D9" s="2">
         <v>32857001</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-005</v>
+      </c>
       <c r="F9" s="2" t="s">
         <v>32</v>
       </c>
@@ -3891,7 +3480,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N9" s="2">
@@ -3907,7 +3496,10 @@
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="E10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-006</v>
+      </c>
       <c r="F10" s="2" t="s">
         <v>44</v>
       </c>
@@ -3926,7 +3518,7 @@
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N10" s="2">
@@ -3948,7 +3540,10 @@
       <c r="D11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-007</v>
+      </c>
       <c r="F11" s="2" t="s">
         <v>48</v>
       </c>
@@ -3967,7 +3562,7 @@
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N11" s="2">
@@ -3989,7 +3584,10 @@
       <c r="D12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-008</v>
+      </c>
       <c r="F12" s="2" t="s">
         <v>52</v>
       </c>
@@ -4008,7 +3606,7 @@
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N12" s="2">
@@ -4030,7 +3628,10 @@
       <c r="D13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-009</v>
+      </c>
       <c r="F13" s="2" t="s">
         <v>55</v>
       </c>
@@ -4049,7 +3650,7 @@
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N13" s="2">
@@ -4071,7 +3672,10 @@
       <c r="D14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-010</v>
+      </c>
       <c r="F14" s="2" t="s">
         <v>59</v>
       </c>
@@ -4090,7 +3694,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N14" s="2">
@@ -4108,7 +3712,10 @@
         <v>61</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-011</v>
+      </c>
       <c r="F15" s="2" t="s">
         <v>62</v>
       </c>
@@ -4127,7 +3734,7 @@
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
       <c r="M15" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N15" s="2">
@@ -4147,7 +3754,10 @@
         <v>50</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-SP-012</v>
+      </c>
       <c r="F16" s="2" t="s">
         <v>64</v>
       </c>
@@ -4166,7 +3776,7 @@
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N16" s="2">
@@ -4188,7 +3798,10 @@
       <c r="D17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-CW-MB-001</v>
+      </c>
       <c r="F17" s="2" t="s">
         <v>67</v>
       </c>
@@ -4207,7 +3820,7 @@
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N17" s="2">
@@ -4229,7 +3842,10 @@
       <c r="D18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="2"/>
+      <c r="E18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-W-SP-001</v>
+      </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
       </c>
@@ -4248,7 +3864,7 @@
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N18" s="2">
@@ -4266,7 +3882,10 @@
       <c r="D19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="10"/>
+      <c r="E19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-W-KT-002</v>
+      </c>
       <c r="F19" s="10" t="s">
         <v>75</v>
       </c>
@@ -4285,7 +3904,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N19" s="2">
@@ -4307,7 +3926,10 @@
       <c r="D20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="10"/>
+      <c r="E20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-W-KT-003</v>
+      </c>
       <c r="F20" s="10" t="s">
         <v>77</v>
       </c>
@@ -4326,7 +3948,7 @@
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N20" s="2">
@@ -4348,7 +3970,10 @@
       <c r="D21" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="10"/>
+      <c r="E21" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-W-KT-004</v>
+      </c>
       <c r="F21" s="10" t="s">
         <v>80</v>
       </c>
@@ -4367,7 +3992,7 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N21" s="2">
@@ -4389,7 +4014,10 @@
       <c r="D22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="10"/>
+      <c r="E22" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-W-SP-004</v>
+      </c>
       <c r="F22" s="10" t="s">
         <v>82</v>
       </c>
@@ -4408,7 +4036,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N22" s="2">
@@ -4426,7 +4054,10 @@
         <v>31</v>
       </c>
       <c r="D23" s="2"/>
-      <c r="E23" s="10"/>
+      <c r="E23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-W-SP-005</v>
+      </c>
       <c r="F23" s="10" t="s">
         <v>82</v>
       </c>
@@ -4445,7 +4076,7 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N23" s="2">
@@ -4465,7 +4096,10 @@
         <v>83</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="E24" s="10"/>
+      <c r="E24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-W-SP-006</v>
+      </c>
       <c r="F24" s="10" t="s">
         <v>84</v>
       </c>
@@ -4484,7 +4118,7 @@
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N24" s="2">
@@ -4506,7 +4140,10 @@
       <c r="D25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="2"/>
+      <c r="E25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN-W-UG-007</v>
+      </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
@@ -4525,7 +4162,7 @@
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
       <c r="M25" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>SN</v>
       </c>
       <c r="N25" s="2">
@@ -4547,7 +4184,10 @@
         <v>90</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="E26" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>EE-SA-HW-8K-001</v>
+      </c>
       <c r="F26" s="2" t="s">
         <v>91</v>
       </c>
@@ -4566,7 +4206,7 @@
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
       <c r="M26" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>EE</v>
       </c>
       <c r="N26" s="2">
@@ -4590,7 +4230,10 @@
       <c r="D27" s="2">
         <v>40367000</v>
       </c>
-      <c r="E27" s="2"/>
+      <c r="E27" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ACT-FT-TPH-001</v>
+      </c>
       <c r="F27" s="2" t="s">
         <v>97</v>
       </c>
@@ -4609,7 +4252,7 @@
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
       <c r="M27" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ACT</v>
       </c>
       <c r="N27" s="2">
@@ -4629,7 +4272,10 @@
         <v>101</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="E28" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ACT-FT-TPH-002</v>
+      </c>
       <c r="F28" s="2" t="s">
         <v>97</v>
       </c>
@@ -4648,7 +4294,7 @@
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ACT</v>
       </c>
       <c r="N28" s="2">
@@ -4672,7 +4318,10 @@
       <c r="D29" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="2"/>
+      <c r="E29" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-W-001</v>
+      </c>
       <c r="F29" s="2" t="s">
         <v>105</v>
       </c>
@@ -4691,7 +4340,7 @@
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
       <c r="M29" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N29" s="2">
@@ -4711,7 +4360,10 @@
       <c r="D30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-W-002</v>
+      </c>
       <c r="F30" s="2" t="s">
         <v>108</v>
       </c>
@@ -4730,7 +4382,7 @@
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
       <c r="M30" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N30" s="2">
@@ -4750,7 +4402,10 @@
       <c r="D31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-W-003</v>
+      </c>
       <c r="F31" s="2" t="s">
         <v>108</v>
       </c>
@@ -4769,7 +4424,7 @@
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
       <c r="M31" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N31" s="2">
@@ -4789,7 +4444,10 @@
       <c r="D32" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E32" s="2"/>
+      <c r="E32" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FT-001</v>
+      </c>
       <c r="F32" s="2" t="s">
         <v>112</v>
       </c>
@@ -4808,7 +4466,7 @@
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
       <c r="M32" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N32" s="2">
@@ -4828,7 +4486,10 @@
       <c r="D33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E33" s="2"/>
+      <c r="E33" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FT-002</v>
+      </c>
       <c r="F33" s="2" t="s">
         <v>114</v>
       </c>
@@ -4847,7 +4508,7 @@
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
       <c r="M33" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N33" s="2">
@@ -4865,7 +4526,10 @@
       <c r="D34" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="2"/>
+      <c r="E34" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FT-003</v>
+      </c>
       <c r="F34" s="2" t="s">
         <v>117</v>
       </c>
@@ -4884,7 +4548,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N34" s="2">
@@ -4906,7 +4570,10 @@
       <c r="D35" s="2">
         <v>930</v>
       </c>
-      <c r="E35" s="2"/>
+      <c r="E35" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FT-004</v>
+      </c>
       <c r="F35" s="2" t="s">
         <v>118</v>
       </c>
@@ -4925,7 +4592,7 @@
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
       <c r="M35" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N35" s="2">
@@ -4947,7 +4614,10 @@
       <c r="D36" s="2">
         <v>318</v>
       </c>
-      <c r="E36" s="2"/>
+      <c r="E36" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FT-005</v>
+      </c>
       <c r="F36" s="2" t="s">
         <v>119</v>
       </c>
@@ -4966,7 +4636,7 @@
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
       <c r="M36" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N36" s="2">
@@ -4990,7 +4660,10 @@
       <c r="D37" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E37" s="2"/>
+      <c r="E37" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FL-001</v>
+      </c>
       <c r="F37" s="2" t="s">
         <v>123</v>
       </c>
@@ -5009,7 +4682,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N37" s="2">
@@ -5029,7 +4702,10 @@
       <c r="D38" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FL-002</v>
+      </c>
       <c r="F38" s="2" t="s">
         <v>128</v>
       </c>
@@ -5048,7 +4724,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N38" s="2">
@@ -5068,7 +4744,10 @@
       <c r="D39" s="2">
         <v>710</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FL-003</v>
+      </c>
       <c r="F39" s="2" t="s">
         <v>131</v>
       </c>
@@ -5087,7 +4766,7 @@
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
       <c r="M39" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N39" s="2">
@@ -5107,7 +4786,10 @@
       <c r="D40" s="2">
         <v>771</v>
       </c>
-      <c r="E40" s="2"/>
+      <c r="E40" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FL-004</v>
+      </c>
       <c r="F40" s="2" t="s">
         <v>132</v>
       </c>
@@ -5126,7 +4808,7 @@
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N40" s="2">
@@ -5146,7 +4828,10 @@
       <c r="D41" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E41" s="2"/>
+      <c r="E41" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FL-005</v>
+      </c>
       <c r="F41" s="2" t="s">
         <v>134</v>
       </c>
@@ -5165,7 +4850,7 @@
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
       <c r="M41" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N41" s="2"/>
@@ -5183,7 +4868,10 @@
       <c r="D42" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FL-006</v>
+      </c>
       <c r="F42" s="2" t="s">
         <v>136</v>
       </c>
@@ -5202,7 +4890,7 @@
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
       <c r="M42" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N42" s="2">
@@ -5220,7 +4908,10 @@
         <v>130</v>
       </c>
       <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+      <c r="E43" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FL-007</v>
+      </c>
       <c r="F43" s="2" t="s">
         <v>138</v>
       </c>
@@ -5239,7 +4930,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N43" s="2">
@@ -5259,7 +4950,10 @@
       <c r="D44" s="2">
         <v>197</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FL-008</v>
+      </c>
       <c r="F44" s="2" t="s">
         <v>141</v>
       </c>
@@ -5278,7 +4972,7 @@
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N44" s="2"/>
@@ -5296,7 +4990,10 @@
       <c r="D45" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FL-009</v>
+      </c>
       <c r="F45" s="2" t="s">
         <v>143</v>
       </c>
@@ -5315,7 +5012,7 @@
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N45" s="2"/>
@@ -5333,7 +5030,10 @@
       <c r="D46" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E46" s="5"/>
+      <c r="E46" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ST-CM-FL-010</v>
+      </c>
       <c r="F46" s="2" t="s">
         <v>146</v>
       </c>
@@ -5346,11 +5046,13 @@
       <c r="I46" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J46" s="5"/>
+      <c r="J46" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ST</v>
       </c>
       <c r="N46" s="2">
@@ -5359,528 +5061,9 @@
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
     </row>
-    <row r="47" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="4"/>
-      <c r="B47" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N47" s="2">
-        <v>0</v>
-      </c>
-      <c r="O47" s="2"/>
-      <c r="P47" s="2"/>
-    </row>
-    <row r="48" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="4"/>
-      <c r="B48" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N48" s="2">
-        <v>0</v>
-      </c>
-      <c r="O48" s="2"/>
-      <c r="P48" s="2"/>
-    </row>
-    <row r="49" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="4"/>
-      <c r="B49" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N49" s="2">
-        <v>1</v>
-      </c>
-      <c r="O49" s="2">
-        <v>0</v>
-      </c>
-      <c r="P49" s="2"/>
-    </row>
-    <row r="50" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="4"/>
-      <c r="B50" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N50" s="2">
-        <v>1</v>
-      </c>
-      <c r="O50" s="2">
-        <v>0</v>
-      </c>
-      <c r="P50" s="2"/>
-    </row>
-    <row r="51" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="4"/>
-      <c r="B51" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N51" s="2">
-        <v>3</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
-    </row>
-    <row r="52" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="4"/>
-      <c r="B52" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" s="2"/>
-    </row>
-    <row r="53" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="4"/>
-      <c r="B53" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N53" s="2">
-        <v>1</v>
-      </c>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
-    </row>
-    <row r="54" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="4"/>
-      <c r="B54" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D54" s="2">
-        <v>8260</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N54" s="2">
-        <v>1</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" s="2"/>
-    </row>
-    <row r="55" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="4"/>
-      <c r="B55" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D55" s="2">
-        <v>8261</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N55" s="2">
-        <v>1</v>
-      </c>
-      <c r="O55" s="2"/>
-      <c r="P55" s="2"/>
-    </row>
-    <row r="56" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="4"/>
-      <c r="B56" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D56" s="2">
-        <v>8260</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N56" s="2">
-        <v>1</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" s="2"/>
-    </row>
-    <row r="57" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="4"/>
-      <c r="B57" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" s="2">
-        <v>7339</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
-      <c r="M57" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N57" s="2">
-        <v>1</v>
-      </c>
-      <c r="O57" s="2"/>
-      <c r="P57" s="2"/>
-    </row>
-    <row r="58" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="4"/>
-      <c r="B58" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D58" s="2">
-        <v>8260</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
-      <c r="M58" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N58" s="2">
-        <v>1</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2"/>
-    </row>
-    <row r="59" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="4"/>
-      <c r="B59" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D59" s="2">
-        <v>8330</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="5"/>
-      <c r="M59" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N59" s="2">
-        <v>1</v>
-      </c>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
-    </row>
-    <row r="60" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="4"/>
-      <c r="B60" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D60" s="2">
-        <v>8290</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
-      <c r="M60" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>ST</v>
-      </c>
-      <c r="N60" s="2">
-        <v>1</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:P60" xr:uid="{27BBB6C5-2512-4B41-B208-AB56387CBE1A}"/>
+  <autoFilter ref="B1:P46" xr:uid="{27BBB6C5-2512-4B41-B208-AB56387CBE1A}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
   <headerFooter>
